--- a/data/trans_orig/IP36BS1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP36BS1-Habitat-trans_orig.xlsx
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>438</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>55,55%</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -7204,12 +7204,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -7882,12 +7882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7952,12 +7952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -8677,12 +8677,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -8790,12 +8790,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -9246,12 +9246,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9316,12 +9316,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -9698,12 +9698,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9713,12 +9713,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9748,12 +9748,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -9811,12 +9811,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9896,12 +9896,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -10267,12 +10267,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>41862</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -10719,12 +10719,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10754,12 +10754,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -10832,12 +10832,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -10945,12 +10945,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -12433,7 +12433,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12498,12 +12498,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12513,12 +12513,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -12541,12 +12541,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12556,12 +12556,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -12993,12 +12993,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -13141,12 +13141,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13176,12 +13176,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13269,12 +13269,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13289,12 +13289,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13304,12 +13304,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -13562,12 +13562,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13632,12 +13632,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>499</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -14240,12 +14240,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14255,12 +14255,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>68,1%</t>
         </is>
       </c>
     </row>
@@ -14583,12 +14583,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14598,12 +14598,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14618,12 +14618,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14633,12 +14633,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14653,12 +14653,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14668,12 +14668,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -14736,7 +14736,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -15035,12 +15035,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15050,12 +15050,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15183,12 +15183,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>864</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>939</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -15261,12 +15261,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15276,12 +15276,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -15296,12 +15296,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15346,12 +15346,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -15604,12 +15604,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15619,12 +15619,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16091,12 +16091,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16106,12 +16106,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16141,12 +16141,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -16169,12 +16169,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16184,12 +16184,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16219,12 +16219,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16254,12 +16254,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -16282,12 +16282,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16297,12 +16297,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16317,12 +16317,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>31113</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16367,12 +16367,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -16970,12 +16970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -16985,12 +16985,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -17040,12 +17040,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -17309,12 +17309,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -17324,12 +17324,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -17344,12 +17344,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -17359,12 +17359,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -17379,12 +17379,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -17394,12 +17394,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,81%</t>
         </is>
       </c>
     </row>
@@ -17422,12 +17422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -17437,12 +17437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -17492,12 +17492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -17507,12 +17507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>54,77%</t>
         </is>
       </c>
     </row>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -17605,12 +17605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -17620,12 +17620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -17953,7 +17953,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -18026,12 +18026,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -18041,12 +18041,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -18061,12 +18061,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -18076,12 +18076,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -18257,7 +18257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -18272,7 +18272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -18292,7 +18292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -18345,12 +18345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -18365,12 +18365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -18380,12 +18380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -18400,12 +18400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -18415,12 +18415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -18448,7 +18448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -18513,12 +18513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -18528,12 +18528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -18899,12 +18899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -18914,12 +18914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -18969,12 +18969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18984,12 +18984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -19012,12 +19012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -19027,12 +19027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -19047,12 +19047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -19062,12 +19062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -19082,12 +19082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17575</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -19097,12 +19097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -19243,7 +19243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -19351,12 +19351,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -19366,12 +19366,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -19421,12 +19421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -19436,12 +19436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -19469,7 +19469,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -19499,12 +19499,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -19514,12 +19514,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -19534,12 +19534,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -19549,12 +19549,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -19612,12 +19612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -19627,12 +19627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -19647,12 +19647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -19662,12 +19662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -19935,12 +19935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19990,12 +19990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -20005,12 +20005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -20033,12 +20033,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>553</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -20048,12 +20048,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -20068,12 +20068,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -20083,12 +20083,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -20103,12 +20103,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -20118,12 +20118,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -20294,12 +20294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -20309,12 +20309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -20329,12 +20329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -20344,12 +20344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -20407,12 +20407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>493</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -20422,12 +20422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -20442,12 +20442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -20457,12 +20457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -20490,7 +20490,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -20520,12 +20520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -20535,12 +20535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -20555,12 +20555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -20570,12 +20570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -20598,12 +20598,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -20613,12 +20613,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -20638,7 +20638,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -20668,12 +20668,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -20683,12 +20683,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -20941,12 +20941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -20956,12 +20956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>394</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20991,12 +20991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -21026,12 +21026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -21069,12 +21069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -21089,12 +21089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -21104,12 +21104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -21124,12 +21124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -21139,12 +21139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -21315,12 +21315,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -21330,12 +21330,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -21350,12 +21350,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -21365,12 +21365,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -21393,12 +21393,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -21408,12 +21408,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -21428,12 +21428,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -21443,12 +21443,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -21463,12 +21463,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -21478,12 +21478,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -21506,12 +21506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -21521,12 +21521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -21556,12 +21556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -21576,12 +21576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -21591,12 +21591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -21619,12 +21619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -21634,12 +21634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -21654,12 +21654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -21669,12 +21669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -21689,12 +21689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -21704,12 +21704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
